--- a/data/raw/weekly.xlsx
+++ b/data/raw/weekly.xlsx
@@ -55632,35 +55632,23 @@
           <t>25-09-2026</t>
         </is>
       </c>
-      <c r="B1292" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C1292" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D1292" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E1292" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F1292" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G1292" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="B1292" s="2" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="C1292" s="2" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="D1292" s="2" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="E1292" s="2" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="F1292" s="2" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="G1292" s="2" t="n">
+        <v>43.35</v>
       </c>
       <c r="H1292" s="2" t="n">
         <v>48.7148</v>
@@ -55687,164 +55675,190 @@
           <t>02-10-2026</t>
         </is>
       </c>
-      <c r="B1293" t="inlineStr">
+      <c r="B1293" s="2" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="C1293" s="2" t="n">
+        <v>43.79</v>
+      </c>
+      <c r="D1293" s="2" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="E1293" s="2" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F1293" s="2" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="G1293" s="2" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H1293" s="2" t="n">
+        <v>48.89618</v>
+      </c>
+      <c r="I1293" s="2" t="n">
+        <v>48.98428</v>
+      </c>
+      <c r="J1293" s="2" t="n">
+        <v>55.51644</v>
+      </c>
+      <c r="K1293" s="2" t="n">
+        <v>55.61648</v>
+      </c>
+      <c r="L1293" s="2" t="n">
+        <v>64.66586</v>
+      </c>
+      <c r="M1293" s="2" t="n">
+        <v>65.003</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>09-10-2026</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="C1293" t="inlineStr">
+      <c r="C1294" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D1293" t="inlineStr">
+      <c r="D1294" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E1293" t="inlineStr">
+      <c r="E1294" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F1293" t="inlineStr">
+      <c r="F1294" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G1293" t="inlineStr">
+      <c r="G1294" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H1293" s="2" t="n">
-        <v>48.7901</v>
-      </c>
-      <c r="I1293" s="2" t="n">
-        <v>48.878</v>
-      </c>
-      <c r="J1293" s="2" t="n">
-        <v>55.5878</v>
-      </c>
-      <c r="K1293" s="2" t="n">
-        <v>55.688</v>
-      </c>
-      <c r="L1293" s="2" t="n">
-        <v>64.4761</v>
-      </c>
-      <c r="M1293" s="2" t="n">
-        <v>64.8122</v>
-      </c>
-    </row>
-    <row r="1294">
-</row>
+      <c r="H1294" s="2" t="n">
+        <v>49.07414</v>
+      </c>
+      <c r="I1294" s="2" t="n">
+        <v>49.16256</v>
+      </c>
+      <c r="J1294" s="2" t="n">
+        <v>55.03802</v>
+      </c>
+      <c r="K1294" s="2" t="n">
+        <v>55.13718</v>
+      </c>
+      <c r="L1294" s="2" t="n">
+        <v>64.77396</v>
+      </c>
+      <c r="M1294" s="2" t="n">
+        <v>65.11164</v>
+      </c>
+    </row>
     <row r="1295">
 </row>
     <row r="1296">
-      <c r="A1296" s="1" t="inlineStr">
+</row>
+    <row r="1297">
+      <c r="A1297" s="1" t="inlineStr">
         <is>
           <t>Seri Açıklamaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1297">
-      <c r="A1297" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT01</t>
-        </is>
-      </c>
-      <c r="B1297" t="inlineStr">
-        <is>
-          <t>1 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>TP.TRY.MT02</t>
+          <t>TP.TRY.MT01</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>3 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>1 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>TP.TRY.MT03</t>
+          <t>TP.TRY.MT02</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>6 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>3 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>TP.TRY.MT04</t>
+          <t>TP.TRY.MT03</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>1 Yıla Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>6 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>TP.TRY.MT05</t>
+          <t>TP.TRY.MT04</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>1 Yıl ve Daha Uzun Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>1 Yıla Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>TP.TRY.MT06</t>
+          <t>TP.TRY.MT05</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Toplam (TL Mevduat, Akım, %)-Düzey</t>
+          <t>1 Yıl ve Daha Uzun Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>TP.DK.USD.A.YTL</t>
+          <t>TP.TRY.MT06</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>(USD)  ABD  Doları  (Döviz  Alış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C1303" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+          <t>Toplam (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>TP.DK.USD.S.YTL</t>
+          <t>TP.DK.USD.A.YTL</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>(USD)  ABD  Doları  (Döviz  Satış)-Düzey</t>
+          <t>(USD)  ABD  Doları  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr">
@@ -55856,12 +55870,12 @@
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.A.YTL</t>
+          <t>TP.DK.USD.S.YTL</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>(EUR)  Euro  (Döviz  Alış)-Düzey</t>
+          <t>(USD)  ABD  Doları  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
@@ -55873,12 +55887,12 @@
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.S.YTL</t>
+          <t>TP.DK.EUR.A.YTL</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>(EUR)  Euro  (Döviz  Satış)-Düzey</t>
+          <t>(EUR)  Euro  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
@@ -55890,12 +55904,12 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.A.YTL</t>
+          <t>TP.DK.EUR.S.YTL</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>(GBP)  İngiliz  Sterlini  (Döviz  Alış)-Düzey</t>
+          <t>(EUR)  Euro  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -55907,56 +55921,60 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
+          <t>TP.DK.GBP.A.YTL</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>(GBP)  İngiliz  Sterlini  (Döviz  Alış)-Düzey</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
           <t>TP.DK.GBP.S.YTL</t>
         </is>
       </c>
-      <c r="B1308" t="inlineStr">
+      <c r="B1309" t="inlineStr">
         <is>
           <t>(GBP)  İngiliz  Sterlini  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
-      <c r="C1308" t="inlineStr">
+      <c r="C1309" t="inlineStr">
         <is>
           <t>Gözlem Değeri: Aritmetik Ortalama</t>
         </is>
       </c>
     </row>
-    <row r="1309">
+    <row r="1310">
 </row>
-    <row r="1310">
-      <c r="A1310" s="1" t="inlineStr">
+    <row r="1311">
+      <c r="A1311" s="1" t="inlineStr">
         <is>
           <t>Notlar</t>
         </is>
       </c>
     </row>
-    <row r="1311">
-      <c r="A1311" t="inlineStr">
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
         <is>
           <t>TP.TRY.MT01</t>
         </is>
       </c>
-      <c r="B1311" t="inlineStr">
+      <c r="B1312" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1311" t="inlineStr">
+      <c r="C1312" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1312">
-      <c r="A1312"/>
-      <c r="B1312" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1312" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -55964,7 +55982,7 @@
       <c r="A1313"/>
       <c r="B1313" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1313" t="inlineStr">
@@ -55977,7 +55995,7 @@
       <c r="A1314"/>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1314" t="inlineStr">
@@ -55990,42 +56008,42 @@
       <c r="A1315"/>
       <c r="B1315" t="inlineStr">
         <is>
+          <t>Revizyon Politika Linki</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316"/>
+      <c r="B1316" t="inlineStr">
+        <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1315" t="inlineStr">
+      <c r="C1316" t="inlineStr">
         <is>
           <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
-    <row r="1316">
-      <c r="A1316" t="inlineStr">
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
         <is>
           <t>TP.TRY.MT02</t>
         </is>
       </c>
-      <c r="B1316" t="inlineStr">
+      <c r="B1317" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1316" t="inlineStr">
+      <c r="C1317" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1317">
-      <c r="A1317"/>
-      <c r="B1317" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1317" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56033,7 +56051,7 @@
       <c r="A1318"/>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
@@ -56046,7 +56064,7 @@
       <c r="A1319"/>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
@@ -56059,42 +56077,42 @@
       <c r="A1320"/>
       <c r="B1320" t="inlineStr">
         <is>
+          <t>Revizyon Politika Linki</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321"/>
+      <c r="B1321" t="inlineStr">
+        <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1320" t="inlineStr">
+      <c r="C1321" t="inlineStr">
         <is>
           <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
-    <row r="1321">
-      <c r="A1321" t="inlineStr">
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
         <is>
           <t>TP.TRY.MT03</t>
         </is>
       </c>
-      <c r="B1321" t="inlineStr">
+      <c r="B1322" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1321" t="inlineStr">
+      <c r="C1322" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1322">
-      <c r="A1322"/>
-      <c r="B1322" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1322" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56102,7 +56120,7 @@
       <c r="A1323"/>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
@@ -56115,7 +56133,7 @@
       <c r="A1324"/>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr">
@@ -56128,42 +56146,42 @@
       <c r="A1325"/>
       <c r="B1325" t="inlineStr">
         <is>
+          <t>Revizyon Politika Linki</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326"/>
+      <c r="B1326" t="inlineStr">
+        <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1325" t="inlineStr">
+      <c r="C1326" t="inlineStr">
         <is>
           <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
-    <row r="1326">
-      <c r="A1326" t="inlineStr">
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
         <is>
           <t>TP.TRY.MT04</t>
         </is>
       </c>
-      <c r="B1326" t="inlineStr">
+      <c r="B1327" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1326" t="inlineStr">
+      <c r="C1327" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1327">
-      <c r="A1327"/>
-      <c r="B1327" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1327" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56171,7 +56189,7 @@
       <c r="A1328"/>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1328" t="inlineStr">
@@ -56184,7 +56202,7 @@
       <c r="A1329"/>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
@@ -56197,42 +56215,42 @@
       <c r="A1330"/>
       <c r="B1330" t="inlineStr">
         <is>
+          <t>Revizyon Politika Linki</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331"/>
+      <c r="B1331" t="inlineStr">
+        <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1330" t="inlineStr">
+      <c r="C1331" t="inlineStr">
         <is>
           <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
-    <row r="1331">
-      <c r="A1331" t="inlineStr">
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
         <is>
           <t>TP.TRY.MT05</t>
         </is>
       </c>
-      <c r="B1331" t="inlineStr">
+      <c r="B1332" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1331" t="inlineStr">
+      <c r="C1332" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1332">
-      <c r="A1332"/>
-      <c r="B1332" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1332" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56240,7 +56258,7 @@
       <c r="A1333"/>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr">
@@ -56253,7 +56271,7 @@
       <c r="A1334"/>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr">
@@ -56266,42 +56284,42 @@
       <c r="A1335"/>
       <c r="B1335" t="inlineStr">
         <is>
+          <t>Revizyon Politika Linki</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336"/>
+      <c r="B1336" t="inlineStr">
+        <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1335" t="inlineStr">
+      <c r="C1336" t="inlineStr">
         <is>
           <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
-    <row r="1336">
-      <c r="A1336" t="inlineStr">
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
         <is>
           <t>TP.TRY.MT06</t>
         </is>
       </c>
-      <c r="B1336" t="inlineStr">
+      <c r="B1337" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1336" t="inlineStr">
+      <c r="C1337" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1337">
-      <c r="A1337"/>
-      <c r="B1337" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1337" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56309,7 +56327,7 @@
       <c r="A1338"/>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr">
@@ -56322,7 +56340,7 @@
       <c r="A1339"/>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr">
@@ -56335,190 +56353,203 @@
       <c r="A1340"/>
       <c r="B1340" t="inlineStr">
         <is>
+          <t>Revizyon Politika Linki</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341"/>
+      <c r="B1341" t="inlineStr">
+        <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1340" t="inlineStr">
+      <c r="C1341" t="inlineStr">
         <is>
           <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
-    <row r="1341">
-      <c r="A1341" t="inlineStr">
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
         <is>
           <t>TP.DK.USD.A.YTL</t>
         </is>
       </c>
-      <c r="B1341" t="inlineStr">
+      <c r="B1342" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1341" t="inlineStr">
+      <c r="C1342" t="inlineStr">
         <is>
           <t>TCMB</t>
         </is>
       </c>
     </row>
-    <row r="1342">
-      <c r="A1342"/>
-      <c r="B1342" t="inlineStr">
+    <row r="1343">
+      <c r="A1343"/>
+      <c r="B1343" t="inlineStr">
         <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1342" t="inlineStr">
+      <c r="C1343" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
       </c>
     </row>
-    <row r="1343">
-      <c r="A1343" t="inlineStr">
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
         <is>
           <t>TP.DK.USD.S.YTL</t>
         </is>
       </c>
-      <c r="B1343" t="inlineStr">
+      <c r="B1344" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1343" t="inlineStr">
+      <c r="C1344" t="inlineStr">
         <is>
           <t>TCMB</t>
         </is>
       </c>
     </row>
-    <row r="1344">
-      <c r="A1344"/>
-      <c r="B1344" t="inlineStr">
+    <row r="1345">
+      <c r="A1345"/>
+      <c r="B1345" t="inlineStr">
         <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1344" t="inlineStr">
+      <c r="C1345" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
       </c>
     </row>
-    <row r="1345">
-      <c r="A1345" t="inlineStr">
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
         <is>
           <t>TP.DK.EUR.A.YTL</t>
         </is>
       </c>
-      <c r="B1345" t="inlineStr">
+      <c r="B1346" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1345" t="inlineStr">
+      <c r="C1346" t="inlineStr">
         <is>
           <t>TCMB</t>
         </is>
       </c>
     </row>
-    <row r="1346">
-      <c r="A1346"/>
-      <c r="B1346" t="inlineStr">
+    <row r="1347">
+      <c r="A1347"/>
+      <c r="B1347" t="inlineStr">
         <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1346" t="inlineStr">
+      <c r="C1347" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
       </c>
     </row>
-    <row r="1347">
-      <c r="A1347" t="inlineStr">
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
         <is>
           <t>TP.DK.EUR.S.YTL</t>
         </is>
       </c>
-      <c r="B1347" t="inlineStr">
+      <c r="B1348" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1347" t="inlineStr">
+      <c r="C1348" t="inlineStr">
         <is>
           <t>TCMB</t>
         </is>
       </c>
     </row>
-    <row r="1348">
-      <c r="A1348"/>
-      <c r="B1348" t="inlineStr">
+    <row r="1349">
+      <c r="A1349"/>
+      <c r="B1349" t="inlineStr">
         <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1348" t="inlineStr">
+      <c r="C1349" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
       </c>
     </row>
-    <row r="1349">
-      <c r="A1349" t="inlineStr">
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
         <is>
           <t>TP.DK.GBP.A.YTL</t>
         </is>
       </c>
-      <c r="B1349" t="inlineStr">
+      <c r="B1350" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1349" t="inlineStr">
+      <c r="C1350" t="inlineStr">
         <is>
           <t>TCMB</t>
         </is>
       </c>
     </row>
-    <row r="1350">
-      <c r="A1350"/>
-      <c r="B1350" t="inlineStr">
+    <row r="1351">
+      <c r="A1351"/>
+      <c r="B1351" t="inlineStr">
         <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1350" t="inlineStr">
+      <c r="C1351" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
       </c>
     </row>
-    <row r="1351">
-      <c r="A1351" t="inlineStr">
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
         <is>
           <t>TP.DK.GBP.S.YTL</t>
         </is>
       </c>
-      <c r="B1351" t="inlineStr">
+      <c r="B1352" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1351" t="inlineStr">
+      <c r="C1352" t="inlineStr">
         <is>
           <t>TCMB</t>
         </is>
       </c>
     </row>
-    <row r="1352">
-      <c r="A1352"/>
-      <c r="B1352" t="inlineStr">
+    <row r="1353">
+      <c r="A1353"/>
+      <c r="B1353" t="inlineStr">
         <is>
           <t>Etiketler</t>
         </is>
       </c>
-      <c r="C1352" t="inlineStr">
+      <c r="C1353" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>

--- a/data/raw/weekly.xlsx
+++ b/data/raw/weekly.xlsx
@@ -55718,35 +55718,23 @@
           <t>09-10-2026</t>
         </is>
       </c>
-      <c r="B1294" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C1294" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D1294" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E1294" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F1294" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G1294" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="B1294" s="2" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="C1294" s="2" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="D1294" s="2" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="E1294" s="2" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="F1294" s="2" t="n">
+        <v>37.57</v>
+      </c>
+      <c r="G1294" s="2" t="n">
+        <v>42.94</v>
       </c>
       <c r="H1294" s="2" t="n">
         <v>49.07414</v>
@@ -55768,131 +55756,207 @@
       </c>
     </row>
     <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>16-10-2026</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H1295" s="2" t="n">
+        <v>49.2579</v>
+      </c>
+      <c r="I1295" s="2" t="n">
+        <v>49.34664</v>
+      </c>
+      <c r="J1295" s="2" t="n">
+        <v>55.16922</v>
+      </c>
+      <c r="K1295" s="2" t="n">
+        <v>55.26862</v>
+      </c>
+      <c r="L1295" s="2" t="n">
+        <v>65.13178</v>
+      </c>
+      <c r="M1295" s="2" t="n">
+        <v>65.47134</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>23-10-2026</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H1296" s="2" t="n">
+        <v>49.3573</v>
+      </c>
+      <c r="I1296" s="2" t="n">
+        <v>49.4463</v>
+      </c>
+      <c r="J1296" s="2" t="n">
+        <v>55.5179</v>
+      </c>
+      <c r="K1296" s="2" t="n">
+        <v>55.618</v>
+      </c>
+      <c r="L1296" s="2" t="n">
+        <v>65.6633</v>
+      </c>
+      <c r="M1296" s="2" t="n">
+        <v>66.0056</v>
+      </c>
+    </row>
+    <row r="1297">
 </row>
-    <row r="1296">
+    <row r="1298">
 </row>
-    <row r="1297">
-      <c r="A1297" s="1" t="inlineStr">
+    <row r="1299">
+      <c r="A1299" s="1" t="inlineStr">
         <is>
           <t>Seri Açıklamaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1298">
-      <c r="A1298" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT01</t>
-        </is>
-      </c>
-      <c r="B1298" t="inlineStr">
-        <is>
-          <t>1 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
-        </is>
-      </c>
-    </row>
-    <row r="1299">
-      <c r="A1299" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT02</t>
-        </is>
-      </c>
-      <c r="B1299" t="inlineStr">
-        <is>
-          <t>3 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>TP.TRY.MT03</t>
+          <t>TP.TRY.MT01</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>6 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>1 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>TP.TRY.MT04</t>
+          <t>TP.TRY.MT02</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
         <is>
-          <t>1 Yıla Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>3 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>TP.TRY.MT05</t>
+          <t>TP.TRY.MT03</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>1 Yıl ve Daha Uzun Vadeli (TL Mevduat, Akım, %)-Düzey</t>
+          <t>6 Aya Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>TP.TRY.MT06</t>
+          <t>TP.TRY.MT04</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Toplam (TL Mevduat, Akım, %)-Düzey</t>
+          <t>1 Yıla Kadar Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>TP.DK.USD.A.YTL</t>
+          <t>TP.TRY.MT05</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>(USD)  ABD  Doları  (Döviz  Alış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C1304" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+          <t>1 Yıl ve Daha Uzun Vadeli (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>TP.DK.USD.S.YTL</t>
+          <t>TP.TRY.MT06</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>(USD)  ABD  Doları  (Döviz  Satış)-Düzey</t>
-        </is>
-      </c>
-      <c r="C1305" t="inlineStr">
-        <is>
-          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+          <t>Toplam (TL Mevduat, Akım, %)-Düzey</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.A.YTL</t>
+          <t>TP.DK.USD.A.YTL</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>(EUR)  Euro  (Döviz  Alış)-Düzey</t>
+          <t>(USD)  ABD  Doları  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
@@ -55904,12 +55968,12 @@
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.S.YTL</t>
+          <t>TP.DK.USD.S.YTL</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
         <is>
-          <t>(EUR)  Euro  (Döviz  Satış)-Düzey</t>
+          <t>(USD)  ABD  Doları  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
       <c r="C1307" t="inlineStr">
@@ -55921,12 +55985,12 @@
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.A.YTL</t>
+          <t>TP.DK.EUR.A.YTL</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>(GBP)  İngiliz  Sterlini  (Döviz  Alış)-Düzey</t>
+          <t>(EUR)  Euro  (Döviz  Alış)-Düzey</t>
         </is>
       </c>
       <c r="C1308" t="inlineStr">
@@ -55938,69 +56002,77 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
+          <t>TP.DK.EUR.S.YTL</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>(EUR)  Euro  (Döviz  Satış)-Düzey</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>TP.DK.GBP.A.YTL</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>(GBP)  İngiliz  Sterlini  (Döviz  Alış)-Düzey</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Gözlem Değeri: Aritmetik Ortalama</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
           <t>TP.DK.GBP.S.YTL</t>
         </is>
       </c>
-      <c r="B1309" t="inlineStr">
+      <c r="B1311" t="inlineStr">
         <is>
           <t>(GBP)  İngiliz  Sterlini  (Döviz  Satış)-Düzey</t>
         </is>
       </c>
-      <c r="C1309" t="inlineStr">
+      <c r="C1311" t="inlineStr">
         <is>
           <t>Gözlem Değeri: Aritmetik Ortalama</t>
         </is>
       </c>
     </row>
-    <row r="1310">
+    <row r="1312">
 </row>
-    <row r="1311">
-      <c r="A1311" s="1" t="inlineStr">
+    <row r="1313">
+      <c r="A1313" s="1" t="inlineStr">
         <is>
           <t>Notlar</t>
         </is>
       </c>
     </row>
-    <row r="1312">
-      <c r="A1312" t="inlineStr">
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
         <is>
           <t>TP.TRY.MT01</t>
         </is>
       </c>
-      <c r="B1312" t="inlineStr">
+      <c r="B1314" t="inlineStr">
         <is>
           <t>Veri Kaynağı</t>
         </is>
       </c>
-      <c r="C1312" t="inlineStr">
+      <c r="C1314" t="inlineStr">
         <is>
           <t>Mevduat Bankaları</t>
-        </is>
-      </c>
-    </row>
-    <row r="1313">
-      <c r="A1313"/>
-      <c r="B1313" t="inlineStr">
-        <is>
-          <t>Uygulama Değişiklik Linki</t>
-        </is>
-      </c>
-      <c r="C1313" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
-        </is>
-      </c>
-    </row>
-    <row r="1314">
-      <c r="A1314"/>
-      <c r="B1314" t="inlineStr">
-        <is>
-          <t>Metodoloji Linki</t>
-        </is>
-      </c>
-      <c r="C1314" t="inlineStr">
-        <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56008,7 +56080,7 @@
       <c r="A1315"/>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr">
@@ -56021,29 +56093,25 @@
       <c r="A1316"/>
       <c r="B1316" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>mevduat, faiz</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
     <row r="1317">
-      <c r="A1317" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT02</t>
-        </is>
-      </c>
+      <c r="A1317"/>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">
         <is>
-          <t>Mevduat Bankaları</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56051,25 +56119,29 @@
       <c r="A1318"/>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Uygulama Değişiklik Linki</t>
+          <t>Etiketler</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
     <row r="1319">
-      <c r="A1319"/>
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>TP.TRY.MT02</t>
+        </is>
+      </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Veri Kaynağı</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>Mevduat Bankaları</t>
         </is>
       </c>
     </row>
@@ -56077,7 +56149,7 @@
       <c r="A1320"/>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
@@ -56090,29 +56162,25 @@
       <c r="A1321"/>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>mevduat, faiz</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
     <row r="1322">
-      <c r="A1322" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT03</t>
-        </is>
-      </c>
+      <c r="A1322"/>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Mevduat Bankaları</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56120,25 +56188,29 @@
       <c r="A1323"/>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Uygulama Değişiklik Linki</t>
+          <t>Etiketler</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
     <row r="1324">
-      <c r="A1324"/>
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>TP.TRY.MT03</t>
+        </is>
+      </c>
       <c r="B1324" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Veri Kaynağı</t>
         </is>
       </c>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>Mevduat Bankaları</t>
         </is>
       </c>
     </row>
@@ -56146,7 +56218,7 @@
       <c r="A1325"/>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1325" t="inlineStr">
@@ -56159,29 +56231,25 @@
       <c r="A1326"/>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>mevduat, faiz</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
     <row r="1327">
-      <c r="A1327" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT04</t>
-        </is>
-      </c>
+      <c r="A1327"/>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>Mevduat Bankaları</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56189,25 +56257,29 @@
       <c r="A1328"/>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>Uygulama Değişiklik Linki</t>
+          <t>Etiketler</t>
         </is>
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
     <row r="1329">
-      <c r="A1329"/>
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>TP.TRY.MT04</t>
+        </is>
+      </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Veri Kaynağı</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>Mevduat Bankaları</t>
         </is>
       </c>
     </row>
@@ -56215,7 +56287,7 @@
       <c r="A1330"/>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr">
@@ -56228,29 +56300,25 @@
       <c r="A1331"/>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>mevduat, faiz</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
     <row r="1332">
-      <c r="A1332" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT05</t>
-        </is>
-      </c>
+      <c r="A1332"/>
       <c r="B1332" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C1332" t="inlineStr">
         <is>
-          <t>Mevduat Bankaları</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56258,25 +56326,29 @@
       <c r="A1333"/>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Uygulama Değişiklik Linki</t>
+          <t>Etiketler</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
     <row r="1334">
-      <c r="A1334"/>
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>TP.TRY.MT05</t>
+        </is>
+      </c>
       <c r="B1334" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Veri Kaynağı</t>
         </is>
       </c>
       <c r="C1334" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>Mevduat Bankaları</t>
         </is>
       </c>
     </row>
@@ -56284,7 +56356,7 @@
       <c r="A1335"/>
       <c r="B1335" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1335" t="inlineStr">
@@ -56297,29 +56369,25 @@
       <c r="A1336"/>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>mevduat, faiz</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
     <row r="1337">
-      <c r="A1337" t="inlineStr">
-        <is>
-          <t>TP.TRY.MT06</t>
-        </is>
-      </c>
+      <c r="A1337"/>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>Mevduat Bankaları</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56327,25 +56395,29 @@
       <c r="A1338"/>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Uygulama Değişiklik Linki</t>
+          <t>Etiketler</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
     <row r="1339">
-      <c r="A1339"/>
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>TP.TRY.MT06</t>
+        </is>
+      </c>
       <c r="B1339" t="inlineStr">
         <is>
-          <t>Metodoloji Linki</t>
+          <t>Veri Kaynağı</t>
         </is>
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
+          <t>Mevduat Bankaları</t>
         </is>
       </c>
     </row>
@@ -56353,7 +56425,7 @@
       <c r="A1340"/>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Revizyon Politika Linki</t>
+          <t>Uygulama Değişiklik Linki</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr">
@@ -56366,29 +56438,25 @@
       <c r="A1341"/>
       <c r="B1341" t="inlineStr">
         <is>
-          <t>Etiketler</t>
+          <t>Metodoloji Linki</t>
         </is>
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>mevduat, faiz</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
     <row r="1342">
-      <c r="A1342" t="inlineStr">
-        <is>
-          <t>TP.DK.USD.A.YTL</t>
-        </is>
-      </c>
+      <c r="A1342"/>
       <c r="B1342" t="inlineStr">
         <is>
-          <t>Veri Kaynağı</t>
+          <t>Revizyon Politika Linki</t>
         </is>
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>TCMB</t>
+          <t>https://www.tcmb.gov.tr/wps/wcm/connect/TR/TCMB+TR/Main+Menu/Istatistikler/Faiz+Istatistikleri/Haftalik/Mevduat+Faiz+Oranlari/</t>
         </is>
       </c>
     </row>
@@ -56401,14 +56469,14 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+          <t>mevduat, faiz</t>
         </is>
       </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>TP.DK.USD.S.YTL</t>
+          <t>TP.DK.USD.A.YTL</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
@@ -56438,7 +56506,7 @@
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.A.YTL</t>
+          <t>TP.DK.USD.S.YTL</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
@@ -56468,7 +56536,7 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>TP.DK.EUR.S.YTL</t>
+          <t>TP.DK.EUR.A.YTL</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
@@ -56498,7 +56566,7 @@
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.A.YTL</t>
+          <t>TP.DK.EUR.S.YTL</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
@@ -56528,7 +56596,7 @@
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>TP.DK.GBP.S.YTL</t>
+          <t>TP.DK.GBP.A.YTL</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
@@ -56550,6 +56618,36 @@
         </is>
       </c>
       <c r="C1353" t="inlineStr">
+        <is>
+          <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>TP.DK.GBP.S.YTL</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Veri Kaynağı</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>TCMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355"/>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Etiketler</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
         <is>
           <t>Kurlar,  Döviz,  Kurları,  Günlük</t>
         </is>
